--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/std/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/ReAct/adaptive/std/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -725,6 +725,228 @@
       <c r="K10" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=0.4,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>35.27</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>88.26000000000001</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>26.03</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.9,scale_th=0.4,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>93.38</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.4,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.2,scale_th=0.4,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>88.13</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>97.77</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>91.98</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>87.83</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>97.56999999999999</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.3,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>92.27</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>97.68000000000001</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>93.38</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.4,type=std</t>
         </is>
       </c>
     </row>
